--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -11236,23 +11236,45 @@
           <t>054</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>bug_mantis</t>
+        </is>
+      </c>
       <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr">
         <is>
           <t>resources/enemy/mon_bug_mantis.webp</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>（待命名）</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>beast</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr"/>
       <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O58" s="4" t="n">
         <v>0</v>
       </c>
@@ -11271,29 +11293,79 @@
       <c r="T58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="4" t="inlineStr"/>
-      <c r="V58" s="4" t="inlineStr"/>
-      <c r="W58" s="4" t="inlineStr"/>
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 9, 9]</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="X58" s="4" t="inlineStr"/>
-      <c r="Y58" s="4" t="inlineStr"/>
-      <c r="Z58" s="4" t="inlineStr"/>
-      <c r="AA58" s="4" t="inlineStr"/>
-      <c r="AB58" s="4" t="inlineStr"/>
-      <c r="AC58" s="4" t="inlineStr"/>
-      <c r="AD58" s="4" t="inlineStr"/>
-      <c r="AE58" s="4" t="inlineStr"/>
-      <c r="AF58" s="4" t="inlineStr"/>
-      <c r="AG58" s="4" t="inlineStr"/>
-      <c r="AH58" s="4" t="inlineStr"/>
-      <c r="AI58" s="4" t="inlineStr"/>
+      <c r="Y58" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG58" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI58" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AJ58" s="4" t="inlineStr"/>
       <c r="AK58" s="4" t="inlineStr"/>
-      <c r="AL58" s="4" t="inlineStr"/>
-      <c r="AM58" s="4" t="inlineStr"/>
-      <c r="AN58" s="4" t="inlineStr"/>
+      <c r="AL58" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AM58" s="4" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="AN58" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
       <c r="AO58" s="4" t="inlineStr"/>
-      <c r="AP58" s="4" t="inlineStr"/>
-      <c r="AQ58" s="4" t="inlineStr"/>
+      <c r="AP58" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AQ58" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="AR58" s="4" t="inlineStr"/>
       <c r="AS58" s="4" t="inlineStr"/>
       <c r="AT58" s="4" t="inlineStr"/>
@@ -11306,7 +11378,11 @@
       <c r="BA58" s="4" t="inlineStr"/>
       <c r="BB58" s="4" t="inlineStr"/>
       <c r="BC58" s="4" t="inlineStr"/>
-      <c r="BD58" s="4" t="inlineStr"/>
+      <c r="BD58" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="74.88" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -11314,23 +11390,45 @@
           <t>055</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>relic_bellascetic</t>
+        </is>
+      </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr">
         <is>
           <t>resources/enemy/mon_relic_bellascetic.webp</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>（待命名）</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>beast</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr"/>
       <c r="M59" s="4" t="inlineStr"/>
-      <c r="N59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O59" s="4" t="n">
         <v>0</v>
       </c>
@@ -11349,29 +11447,79 @@
       <c r="T59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="4" t="inlineStr"/>
-      <c r="V59" s="4" t="inlineStr"/>
-      <c r="W59" s="4" t="inlineStr"/>
+      <c r="U59" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 9, 9]</t>
+        </is>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="X59" s="4" t="inlineStr"/>
-      <c r="Y59" s="4" t="inlineStr"/>
-      <c r="Z59" s="4" t="inlineStr"/>
-      <c r="AA59" s="4" t="inlineStr"/>
-      <c r="AB59" s="4" t="inlineStr"/>
-      <c r="AC59" s="4" t="inlineStr"/>
-      <c r="AD59" s="4" t="inlineStr"/>
-      <c r="AE59" s="4" t="inlineStr"/>
-      <c r="AF59" s="4" t="inlineStr"/>
-      <c r="AG59" s="4" t="inlineStr"/>
-      <c r="AH59" s="4" t="inlineStr"/>
-      <c r="AI59" s="4" t="inlineStr"/>
+      <c r="Y59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG59" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AJ59" s="4" t="inlineStr"/>
       <c r="AK59" s="4" t="inlineStr"/>
-      <c r="AL59" s="4" t="inlineStr"/>
-      <c r="AM59" s="4" t="inlineStr"/>
-      <c r="AN59" s="4" t="inlineStr"/>
+      <c r="AL59" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AM59" s="4" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="AN59" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
       <c r="AO59" s="4" t="inlineStr"/>
-      <c r="AP59" s="4" t="inlineStr"/>
-      <c r="AQ59" s="4" t="inlineStr"/>
+      <c r="AP59" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AQ59" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="AR59" s="4" t="inlineStr"/>
       <c r="AS59" s="4" t="inlineStr"/>
       <c r="AT59" s="4" t="inlineStr"/>
@@ -11384,7 +11532,11 @@
       <c r="BA59" s="4" t="inlineStr"/>
       <c r="BB59" s="4" t="inlineStr"/>
       <c r="BC59" s="4" t="inlineStr"/>
-      <c r="BD59" s="4" t="inlineStr"/>
+      <c r="BD59" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="74.88" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -11392,23 +11544,45 @@
           <t>056</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>rictus_hooked</t>
+        </is>
+      </c>
       <c r="C60" s="4" t="inlineStr"/>
       <c r="D60" s="4" t="inlineStr">
         <is>
           <t>resources/enemy/mon_rictus_hooked.webp</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>（待命名）</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>beast</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr"/>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
@@ -11427,29 +11601,79 @@
       <c r="T60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="4" t="inlineStr"/>
-      <c r="V60" s="4" t="inlineStr"/>
-      <c r="W60" s="4" t="inlineStr"/>
+      <c r="U60" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 9, 9]</t>
+        </is>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="X60" s="4" t="inlineStr"/>
-      <c r="Y60" s="4" t="inlineStr"/>
-      <c r="Z60" s="4" t="inlineStr"/>
-      <c r="AA60" s="4" t="inlineStr"/>
-      <c r="AB60" s="4" t="inlineStr"/>
-      <c r="AC60" s="4" t="inlineStr"/>
-      <c r="AD60" s="4" t="inlineStr"/>
-      <c r="AE60" s="4" t="inlineStr"/>
-      <c r="AF60" s="4" t="inlineStr"/>
-      <c r="AG60" s="4" t="inlineStr"/>
-      <c r="AH60" s="4" t="inlineStr"/>
-      <c r="AI60" s="4" t="inlineStr"/>
+      <c r="Y60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF60" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG60" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI60" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AJ60" s="4" t="inlineStr"/>
       <c r="AK60" s="4" t="inlineStr"/>
-      <c r="AL60" s="4" t="inlineStr"/>
-      <c r="AM60" s="4" t="inlineStr"/>
-      <c r="AN60" s="4" t="inlineStr"/>
+      <c r="AL60" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AM60" s="4" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="AN60" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
       <c r="AO60" s="4" t="inlineStr"/>
-      <c r="AP60" s="4" t="inlineStr"/>
-      <c r="AQ60" s="4" t="inlineStr"/>
+      <c r="AP60" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AQ60" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="AR60" s="4" t="inlineStr"/>
       <c r="AS60" s="4" t="inlineStr"/>
       <c r="AT60" s="4" t="inlineStr"/>
@@ -11462,7 +11686,11 @@
       <c r="BA60" s="4" t="inlineStr"/>
       <c r="BB60" s="4" t="inlineStr"/>
       <c r="BC60" s="4" t="inlineStr"/>
-      <c r="BD60" s="4" t="inlineStr"/>
+      <c r="BD60" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -13891,7 +14119,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>7b730ea0ee0c856c8630e98ca83709fb35e2662911d46a67c3eb4eef5e063274</t>
+          <t>46df6af89a6313b0b68b0092116f305b249a39062eb0e6427f3a82cde874abf7</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -4661,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
@@ -4822,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
@@ -6112,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="4" t="b">
         <v>1</v>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>74f847d6c9c55d02e1cdba6844bf55591bf098ad5e72e0a078d018fe3d3ea6f3</t>
+          <t>6af6db9db55fe35ef4c75bbfb7aa258c027b2e5e1fbfd79125f28905062bb97a</t>
         </is>
       </c>
     </row>
